--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487765_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487765_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9061</v>
+        <v>4.0492</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8718</v>
+        <v>3.0442</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0343</v>
+        <v>1.0049</v>
       </c>
       <c r="G2" t="n">
         <v>3.4661</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0457</v>
+        <v>0.1887</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3295</v>
+        <v>-0.1571</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3752</v>
+        <v>0.3458</v>
       </c>
       <c r="V2" t="n">
         <v>-0.23</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4506</v>
+        <v>3.9944</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9001</v>
+        <v>3.1797</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5504</v>
+        <v>0.8147</v>
       </c>
       <c r="G3" t="n">
         <v>0.2898</v>
@@ -688,13 +688,13 @@
         <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7372</v>
+        <v>-0.1935</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.3762</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0815</v>
+        <v>0.1827</v>
       </c>
       <c r="V3" t="n">
         <v>2.4412</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6671</v>
+        <v>2.8116</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0197</v>
+        <v>0.8707</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6473</v>
+        <v>1.9409</v>
       </c>
       <c r="G4" t="n">
         <v>-1.1144</v>
@@ -766,13 +766,13 @@
         <v>2.4974</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2643</v>
+        <v>-0.1197</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2023</v>
+        <v>-0.3514</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0619</v>
+        <v>0.2317</v>
       </c>
       <c r="V4" t="n">
         <v>4.6701</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2869</v>
+        <v>2.4029</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4361</v>
+        <v>1.7575</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8509</v>
+        <v>0.6454</v>
       </c>
       <c r="G5" t="n">
         <v>2.0381</v>
@@ -844,13 +844,13 @@
         <v>2.4974</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2923</v>
+        <v>-0.1763</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5905</v>
+        <v>-0.269</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2982</v>
+        <v>0.0927</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7076</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9188</v>
+        <v>1.5055</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9023</v>
+        <v>1.7532</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0165</v>
+        <v>-0.2477</v>
       </c>
       <c r="G6" t="n">
         <v>2.3178</v>
@@ -922,13 +922,13 @@
         <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1254</v>
+        <v>0.7121</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0033</v>
+        <v>-0.1524</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1287</v>
+        <v>0.8645</v>
       </c>
       <c r="V6" t="n">
         <v>-2.565</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0404</v>
+        <v>0.7087</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1251</v>
+        <v>-0.3394</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1655</v>
+        <v>1.0481</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5152</v>
@@ -1000,13 +1000,13 @@
         <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2851</v>
+        <v>-0.0467</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0033</v>
+        <v>-0.2176</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2884</v>
+        <v>0.171</v>
       </c>
       <c r="V7" t="n">
         <v>0.23</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SAKHO</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2735</v>
+        <v>-0.445</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5631</v>
+        <v>-0.8449</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2896</v>
+        <v>0.3999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3176</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9169</v>
+        <v>0.0939</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.7144</v>
       </c>
       <c r="J8" t="n">
-        <v>0.285</v>
+        <v>-0.7144</v>
       </c>
       <c r="K8" t="n">
-        <v>0.921</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.636</v>
+        <v>-0.7144</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0326</v>
+        <v>0.0939</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0041</v>
+        <v>0.0939</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0367</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2081</v>
+        <v>0.2081</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0145</v>
+        <v>-0.0326</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1924</v>
+        <v>-0.1305</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.0979</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>M. SAKHO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5037</v>
+        <v>-0.6155</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8449</v>
+        <v>-0.6703</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3411</v>
+        <v>0.0548</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6205000000000001</v>
+        <v>0.3176</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0939</v>
+        <v>0.9169</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7144</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7144</v>
+        <v>0.285</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.921</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7144</v>
+        <v>-0.636</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0939</v>
+        <v>0.0326</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0939</v>
+        <v>-0.0041</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.0367</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2081</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.6725</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1305</v>
+        <v>0.0853</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0391</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2935</v>
+        <v>-1.7475</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9911</v>
+        <v>-1.5625</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3024</v>
+        <v>-0.185</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4248</v>
@@ -1234,13 +1234,13 @@
         <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9499</v>
+        <v>-0.4038</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7829</v>
+        <v>-0.3543</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.167</v>
+        <v>-0.0496</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1675</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6674</v>
+        <v>-6.8061</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3613</v>
+        <v>-6.6175</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3061</v>
+        <v>-0.1887</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1832</v>
@@ -1312,13 +1312,13 @@
         <v>2.4974</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.276</v>
+        <v>-0.4148</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1371</v>
+        <v>-0.3933</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1389</v>
+        <v>-0.0215</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3351</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.531800000000001</v>
+        <v>5.858199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2445000000000013</v>
+        <v>0.5707000000000004</v>
       </c>
       <c r="F12" t="n">
-        <v>5.2871</v>
+        <v>5.2873</v>
       </c>
       <c r="G12" t="n">
         <v>2.571299999999999</v>
@@ -1390,10 +1390,10 @@
         <v>15.6088</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1403000000000001</v>
+        <v>0.1858999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.6427</v>
+        <v>-2.3165</v>
       </c>
       <c r="U12" t="n">
         <v>2.5024</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3024</v>
+        <v>7.1905</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8886</v>
+        <v>4.4244</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4137</v>
+        <v>2.766</v>
       </c>
       <c r="G13" t="n">
         <v>3.808</v>
@@ -1468,13 +1468,13 @@
         <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1691</v>
+        <v>-0.281</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9786</v>
+        <v>-0.4429</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1904</v>
+        <v>0.1619</v>
       </c>
       <c r="V13" t="n">
         <v>3.0391</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6699</v>
+        <v>2.4747</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2547</v>
+        <v>3.1475</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5848</v>
+        <v>-0.6728</v>
       </c>
       <c r="G14" t="n">
         <v>5.0675</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2303</v>
+        <v>0.0351</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2643</v>
+        <v>-0.3714</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4946</v>
+        <v>0.4065</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1711</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BIRD-JELINEK</t>
+          <t>S. SERRATO BALLETBO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.2055</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3247</v>
+        <v>0.7651</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4001</v>
+        <v>-0.5596</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.554</v>
+        <v>-0.2262</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2943</v>
+        <v>-0.3944</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8483000000000001</v>
+        <v>0.1682</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1729</v>
+        <v>0.7046</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6332</v>
+        <v>0.0384</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5396</v>
+        <v>0.6662</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7268</v>
+        <v>-0.9308</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3389</v>
+        <v>-0.4328</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3879</v>
+        <v>-0.498</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.4162</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3953</v>
+        <v>0.0155</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1924</v>
+        <v>0.0605</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2029</v>
+        <v>-0.045</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. SERRATO BALLETBO</t>
+          <t>A. BIRD-JELINEK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1747</v>
+        <v>-0.3675</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4436</v>
+        <v>0.0032</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6183</v>
+        <v>-0.3707</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2262</v>
+        <v>-0.554</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3944</v>
+        <v>0.2943</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1682</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7046</v>
+        <v>1.1729</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0384</v>
+        <v>0.6332</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6662</v>
+        <v>0.5396</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9308</v>
+        <v>-1.7268</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4328</v>
+        <v>-0.3389</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.498</v>
+        <v>-1.3879</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
         <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3647</v>
+        <v>0.1032</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.261</v>
+        <v>-0.129</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1037</v>
+        <v>0.2323</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8152</v>
+        <v>-0.6097</v>
       </c>
       <c r="E17" t="n">
         <v>1.8475</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6627</v>
+        <v>-2.4572</v>
       </c>
       <c r="G17" t="n">
         <v>0.0016</v>
@@ -1780,13 +1780,13 @@
         <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0183</v>
+        <v>0.1873</v>
       </c>
       <c r="T17" t="n">
         <v>0.1272</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1454</v>
+        <v>0.0601</v>
       </c>
       <c r="V17" t="n">
         <v>-1.631</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9205</v>
+        <v>-0.8633</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3464</v>
+        <v>-1.025</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4259</v>
+        <v>0.1617</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9965</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2186</v>
+        <v>0.2758</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5219</v>
+        <v>-0.2005</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7405</v>
+        <v>0.4763</v>
       </c>
       <c r="V18" t="n">
         <v>1.2737</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. AREVALO SAENZ</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.465</v>
+        <v>-1.4578</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.5262</v>
+        <v>-3.3899</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0612</v>
+        <v>1.9322</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5895</v>
+        <v>-1.2831</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.5568</v>
+        <v>-1.7207</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0326</v>
+        <v>0.4376</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.8545</v>
+        <v>-1.9688</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.9239</v>
+        <v>-1.3328</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0694</v>
+        <v>-0.636</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.735</v>
+        <v>0.6857</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6329</v>
+        <v>-0.3879</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.102</v>
+        <v>1.0736</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2893</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8731</v>
+        <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2494</v>
+        <v>-0.3828</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4501</v>
+        <v>-0.6105</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7993</v>
+        <v>0.2277</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2914</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1238</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>B. AREVALO SAENZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.653</v>
+        <v>-2.1769</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4971</v>
+        <v>-4.0619</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8441</v>
+        <v>1.885</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2831</v>
+        <v>-3.5895</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7207</v>
+        <v>-3.5568</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4376</v>
+        <v>-0.0326</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9688</v>
+        <v>-2.8545</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3328</v>
+        <v>-2.9239</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.636</v>
+        <v>0.0694</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6857</v>
+        <v>-0.735</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3879</v>
+        <v>-0.6329</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0736</v>
+        <v>-0.102</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-2.2893</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.578</v>
+        <v>0.5374</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7177</v>
+        <v>-0.0857</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1397</v>
+        <v>0.6231</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2914</v>
       </c>
       <c r="W20" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3029</v>
+        <v>-2.2736</v>
       </c>
       <c r="E21" t="n">
         <v>-1.6897</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6132</v>
+        <v>-0.5838</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0615</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2414</v>
+        <v>-0.212</v>
       </c>
       <c r="T21" t="n">
         <v>-0.261</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2193</v>
+        <v>-2.7598</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5328</v>
+        <v>-2.4256</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6865</v>
+        <v>-0.3342</v>
       </c>
       <c r="G22" t="n">
         <v>1.0287</v>
@@ -2170,13 +2170,13 @@
         <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3277</v>
+        <v>-0.8682</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9134</v>
+        <v>-0.8062</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4143</v>
+        <v>-0.0619</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0472</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8782</v>
+        <v>-4.894</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4542</v>
+        <v>-2.8828</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.424</v>
+        <v>-2.0112</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7662</v>
@@ -2248,13 +2248,13 @@
         <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>1.7459</v>
+        <v>0.7301</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6458</v>
+        <v>0.2172</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1</v>
+        <v>0.5129</v>
       </c>
       <c r="V23" t="n">
         <v>-1.401</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.531899999999999</v>
+        <v>-5.5319</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2873</v>
+        <v>-5.2872</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2446999999999999</v>
+        <v>-0.2446000000000002</v>
       </c>
       <c r="G24" t="n">
         <v>-2.571200000000002</v>
@@ -2326,10 +2326,10 @@
         <v>11.4466</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1402999999999999</v>
+        <v>0.1403999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.5024</v>
+        <v>-2.5023</v>
       </c>
       <c r="U24" t="n">
         <v>2.6428</v>
